--- a/data/trans_orig/P05A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P05A_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>297491</t>
+          <t>297303</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>356810</t>
+          <t>356537</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>415530</t>
+          <t>422031</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>487237</t>
+          <t>491386</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>731934</t>
+          <t>730694</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>821376</t>
+          <t>821946</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,02%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>674913</t>
+          <t>675186</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>734232</t>
+          <t>734420</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>827876</t>
+          <t>823727</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>899583</t>
+          <t>893082</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1525459</t>
+          <t>1524889</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1614901</t>
+          <t>1616141</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,86%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>424326</t>
+          <t>426574</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>498854</t>
+          <t>501106</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>511701</t>
+          <t>515273</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>588899</t>
+          <t>592092</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>957024</t>
+          <t>958277</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1064701</t>
+          <t>1064932</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1194559</t>
+          <t>1192307</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1269087</t>
+          <t>1266839</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>998774</t>
+          <t>995581</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1075972</t>
+          <t>1072400</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2216385</t>
+          <t>2216154</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2324062</t>
+          <t>2322809</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>70,79%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>157363</t>
+          <t>158729</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>202232</t>
+          <t>202781</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>139263</t>
+          <t>138120</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>179776</t>
+          <t>179576</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>308268</t>
+          <t>306033</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>370604</t>
+          <t>369168</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,92%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>349176</t>
+          <t>348627</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>394045</t>
+          <t>392679</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>296636</t>
+          <t>296836</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>337149</t>
+          <t>338292</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>657216</t>
+          <t>658652</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>719552</t>
+          <t>721787</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,23%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>919208</t>
+          <t>920308</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1028197</t>
+          <t>1021510</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1107855</t>
+          <t>1111094</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1219558</t>
+          <t>1220849</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2057115</t>
+          <t>2048095</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2216172</t>
+          <t>2207510</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,17%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2248346</t>
+          <t>2255033</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2357335</t>
+          <t>2356235</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2159639</t>
+          <t>2158348</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2271342</t>
+          <t>2268103</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4439569</t>
+          <t>4448231</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4598626</t>
+          <t>4607646</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,23%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>342430</t>
+          <t>341210</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>403686</t>
+          <t>404616</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>492046</t>
+          <t>489938</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>566729</t>
+          <t>566738</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>855200</t>
+          <t>852125</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>951585</t>
+          <t>953291</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,26%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>569789</t>
+          <t>568859</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>631045</t>
+          <t>632265</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>770111</t>
+          <t>770102</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>844794</t>
+          <t>846902</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1358731</t>
+          <t>1357025</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1455116</t>
+          <t>1458191</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,12%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>725273</t>
+          <t>727707</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>817537</t>
+          <t>815261</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>642529</t>
+          <t>643797</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>728459</t>
+          <t>729018</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1396304</t>
+          <t>1395059</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1519397</t>
+          <t>1520122</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1142901</t>
+          <t>1145177</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1235165</t>
+          <t>1232731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1024449</t>
+          <t>1023890</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1110379</t>
+          <t>1109111</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2193949</t>
+          <t>2193224</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2317042</t>
+          <t>2318287</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,43%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>189964</t>
+          <t>189138</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>233925</t>
+          <t>235934</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>178810</t>
+          <t>178763</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>225779</t>
+          <t>221669</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>378018</t>
+          <t>379351</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>444165</t>
+          <t>441369</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>46,96%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>247256</t>
+          <t>245247</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>291217</t>
+          <t>292043</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>232852</t>
+          <t>236962</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>279821</t>
+          <t>279868</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>495648</t>
+          <t>498444</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>561795</t>
+          <t>560462</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,64%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1299131</t>
+          <t>1296621</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1414561</t>
+          <t>1416877</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1350049</t>
+          <t>1354515</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1473815</t>
+          <t>1474670</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2679065</t>
+          <t>2687504</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2858479</t>
+          <t>2860421</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,08%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2000534</t>
+          <t>1998218</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2115964</t>
+          <t>2118474</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2074564</t>
+          <t>2073709</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2198330</t>
+          <t>2193864</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4104995</t>
+          <t>4103053</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4284409</t>
+          <t>4275970</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,41%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>246562</t>
+          <t>247689</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>299535</t>
+          <t>300797</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>308073</t>
+          <t>307906</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>370918</t>
+          <t>371426</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>570882</t>
+          <t>570316</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>659272</t>
+          <t>654072</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,45%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>454812</t>
+          <t>453550</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>507785</t>
+          <t>506658</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>621436</t>
+          <t>620928</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>684281</t>
+          <t>684448</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1087429</t>
+          <t>1092629</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1175819</t>
+          <t>1176385</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,35%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>677179</t>
+          <t>670982</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>762703</t>
+          <t>762137</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>684780</t>
+          <t>683649</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>771487</t>
+          <t>770880</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1388852</t>
+          <t>1389738</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1510167</t>
+          <t>1516896</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1312415</t>
+          <t>1312981</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1397939</t>
+          <t>1404136</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1216813</t>
+          <t>1217420</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1303520</t>
+          <t>1304651</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2553251</t>
+          <t>2546522</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2674566</t>
+          <t>2673680</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,8%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>197247</t>
+          <t>197555</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>243038</t>
+          <t>245669</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>203523</t>
+          <t>204424</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>249171</t>
+          <t>247769</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>414553</t>
+          <t>414137</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>481062</t>
+          <t>477228</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,54%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>303848</t>
+          <t>301217</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>349639</t>
+          <t>349331</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>299969</t>
+          <t>301371</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>345617</t>
+          <t>344716</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>614965</t>
+          <t>618799</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>681474</t>
+          <t>681890</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,21%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1160109</t>
+          <t>1160086</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1272843</t>
+          <t>1273424</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1237743</t>
+          <t>1241813</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1355712</t>
+          <t>1354446</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2431406</t>
+          <t>2433084</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2590133</t>
+          <t>2593301</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,55%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2103508</t>
+          <t>2102927</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2216242</t>
+          <t>2216265</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2174082</t>
+          <t>2175348</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2292051</t>
+          <t>2287981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4316012</t>
+          <t>4312844</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4474739</t>
+          <t>4473061</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,77%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>101523</t>
+          <t>111649</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85217</t>
+          <t>95028</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>118925</t>
+          <t>132997</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>134597</t>
+          <t>149072</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>118904</t>
+          <t>131959</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>151749</t>
+          <t>166641</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>236121</t>
+          <t>260720</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>211697</t>
+          <t>235632</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>258495</t>
+          <t>287997</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>413415</t>
+          <t>466880</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>396013</t>
+          <t>445532</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>429721</t>
+          <t>483501</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>620911</t>
+          <t>672966</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>603759</t>
+          <t>655397</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>636604</t>
+          <t>690079</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1034325</t>
+          <t>1139847</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1011951</t>
+          <t>1112570</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1058749</t>
+          <t>1164935</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,18%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>342219</t>
+          <t>382591</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>235423</t>
+          <t>343268</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>400687</t>
+          <t>423826</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>581688</t>
+          <t>434088</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>401533</t>
+          <t>402124</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>985696</t>
+          <t>471309</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>923907</t>
+          <t>816680</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>709345</t>
+          <t>763219</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1504636</t>
+          <t>870580</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1948108</t>
+          <t>1847975</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1889640</t>
+          <t>1806740</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2054904</t>
+          <t>1887298</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1656135</t>
+          <t>1737304</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1252127</t>
+          <t>1700083</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1836290</t>
+          <t>1769268</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3604243</t>
+          <t>3585279</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3023514</t>
+          <t>3531379</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3818805</t>
+          <t>3638740</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>82,66%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>149164</t>
+          <t>158770</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>126966</t>
+          <t>135457</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>176313</t>
+          <t>186935</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>156111</t>
+          <t>174900</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>135786</t>
+          <t>154863</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>177206</t>
+          <t>196042</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>305275</t>
+          <t>333671</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>274445</t>
+          <t>302813</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>338079</t>
+          <t>368402</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>497459</t>
+          <t>552817</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>470310</t>
+          <t>524652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>519657</t>
+          <t>576130</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>503010</t>
+          <t>558546</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>481915</t>
+          <t>537404</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>523335</t>
+          <t>578583</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1000469</t>
+          <t>1111362</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>967665</t>
+          <t>1076631</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1031299</t>
+          <t>1142220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>79,04%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>659121</t>
+          <t>733446</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>659121</t>
+          <t>733446</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>659121</t>
+          <t>733446</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1305744</t>
+          <t>1445033</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1305744</t>
+          <t>1445033</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1305744</t>
+          <t>1445033</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>592906</t>
+          <t>653010</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>466683</t>
+          <t>600166</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>660714</t>
+          <t>703398</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>872396</t>
+          <t>758060</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>686178</t>
+          <t>712946</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1371085</t>
+          <t>805658</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1465302</t>
+          <t>1411071</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1260444</t>
+          <t>1347450</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2136042</t>
+          <t>1480141</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2858983</t>
+          <t>2867673</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2791175</t>
+          <t>2817285</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2985206</t>
+          <t>2920517</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2780056</t>
+          <t>2968816</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2281367</t>
+          <t>2921218</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2966274</t>
+          <t>3013930</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5639039</t>
+          <t>5836488</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4968299</t>
+          <t>5767418</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5843897</t>
+          <t>5900109</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>81,41%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3652452</t>
+          <t>3726876</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3652452</t>
+          <t>3726876</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3652452</t>
+          <t>3726876</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7104341</t>
+          <t>7247559</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7104341</t>
+          <t>7247559</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7104341</t>
+          <t>7247559</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
